--- a/neet_exam_dataset_updated.xlsx
+++ b/neet_exam_dataset_updated.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Zaki DA\Excel-Data-Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2815D521-9DBF-4FA4-8C3A-232BC88598B3}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89F988A2-7476-48EA-A018-6EB4832CDF35}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7005" tabRatio="815" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7005" tabRatio="815" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="neet_exam_dataset_updated" sheetId="1" r:id="rId1"/>
@@ -18,17 +18,18 @@
     <sheet name="Pivot Table" sheetId="4" r:id="rId3"/>
     <sheet name="Analysis" sheetId="3" r:id="rId4"/>
     <sheet name="Dash-Board " sheetId="6" r:id="rId5"/>
-    <sheet name="Rough Work" sheetId="5" r:id="rId6"/>
+    <sheet name="Speedo-Meter" sheetId="7" r:id="rId6"/>
+    <sheet name="Rough Work" sheetId="5" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="1" r:id="rId7"/>
+    <pivotCache cacheId="0" r:id="rId8"/>
   </pivotCaches>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5291" uniqueCount="1075">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5302" uniqueCount="1085">
   <si>
     <t>Seat_No</t>
   </si>
@@ -3253,6 +3254,36 @@
   </si>
   <si>
     <t>Age of Student</t>
+  </si>
+  <si>
+    <t>Slice_1</t>
+  </si>
+  <si>
+    <t>Slice_2</t>
+  </si>
+  <si>
+    <t>Slice_3</t>
+  </si>
+  <si>
+    <t>Slice_4</t>
+  </si>
+  <si>
+    <t>Slice_5</t>
+  </si>
+  <si>
+    <t>Slice_6</t>
+  </si>
+  <si>
+    <t>Tatal</t>
+  </si>
+  <si>
+    <t>Width</t>
+  </si>
+  <si>
+    <t>Value</t>
+  </si>
+  <si>
+    <t>Total</t>
   </si>
 </sst>
 </file>
@@ -5509,6 +5540,331 @@
 </c:chartSpace>
 </file>
 
+<file path=xl/charts/chart12.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:autoTitleDeleted val="1"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:doughnutChart>
+        <c:varyColors val="1"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:dPt>
+            <c:idx val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="1"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="2"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="3"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="4"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent5"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="5"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent6"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="6"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000001-20F1-4EEF-95CC-302D54D830B1}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:val>
+            <c:numRef>
+              <c:f>'Speedo-Meter'!$C$2:$C$8</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>25</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>100</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>160</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>345</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-20F1-4EEF-95CC-302D54D830B1}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:showLeaderLines val="1"/>
+        </c:dLbls>
+        <c:firstSliceAng val="270"/>
+        <c:holeSize val="75"/>
+      </c:doughnutChart>
+      <c:pieChart>
+        <c:varyColors val="1"/>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:v>Pointer</c:v>
+          </c:tx>
+          <c:dPt>
+            <c:idx val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000000A-20F1-4EEF-95CC-302D54D830B1}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="1"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="2"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000009-20F1-4EEF-95CC-302D54D830B1}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:val>
+            <c:numRef>
+              <c:f>'Speedo-Meter'!$F$2:$F$4</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>200</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>325</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000008-20F1-4EEF-95CC-302D54D830B1}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:showLeaderLines val="1"/>
+        </c:dLbls>
+        <c:firstSliceAng val="270"/>
+      </c:pieChart>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+  <c:userShapes r:id="rId3"/>
+</c:chartSpace>
+</file>
+
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
@@ -6660,6 +7016,47 @@
         <c:marker>
           <c:symbol val="none"/>
         </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
       </c:pivotFmt>
       <c:pivotFmt>
         <c:idx val="1"/>
@@ -6695,23 +7092,22 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="1500" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
-                      <a:schemeClr val="bg1"/>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
                     </a:solidFill>
                     <a:latin typeface="+mn-lt"/>
                     <a:ea typeface="+mn-ea"/>
                     <a:cs typeface="+mn-cs"/>
                   </a:defRPr>
                 </a:pPr>
-                <a:fld id="{B7281AA5-CFE2-4A22-A6FE-06753E3138AF}" type="CELLRANGE">
-                  <a:rPr lang="en-US"/>
+                <a:fld id="{80A53F31-036F-47F7-9535-481A93ADA2D9}" type="CELLRANGE">
+                  <a:rPr lang="en-US" baseline="0"/>
                   <a:pPr>
-                    <a:defRPr sz="1500" b="1">
-                      <a:solidFill>
-                        <a:schemeClr val="bg1"/>
-                      </a:solidFill>
-                    </a:defRPr>
+                    <a:defRPr/>
                   </a:pPr>
                   <a:t>[CELLRANGE]</a:t>
                 </a:fld>
@@ -6719,14 +7115,10 @@
                   <a:rPr lang="en-US" baseline="0"/>
                   <a:t>:</a:t>
                 </a:r>
-                <a:fld id="{68246D07-8DB1-4D7F-9318-0C774C1DC43B}" type="VALUE">
+                <a:fld id="{3D1BF7A5-7952-48D6-A5EE-01AF6EDB3A5A}" type="VALUE">
                   <a:rPr lang="en-US" baseline="0"/>
                   <a:pPr>
-                    <a:defRPr sz="1500" b="1">
-                      <a:solidFill>
-                        <a:schemeClr val="bg1"/>
-                      </a:solidFill>
-                    </a:defRPr>
+                    <a:defRPr/>
                   </a:pPr>
                   <a:t>[VALUE]</a:t>
                 </a:fld>
@@ -6748,9 +7140,12 @@
             <a:lstStyle/>
             <a:p>
               <a:pPr>
-                <a:defRPr sz="1500" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                   <a:solidFill>
-                    <a:schemeClr val="bg1"/>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
                   </a:solidFill>
                   <a:latin typeface="+mn-lt"/>
                   <a:ea typeface="+mn-ea"/>
@@ -6800,97 +7195,6 @@
             </a:contourClr>
           </a:sp3d>
         </c:spPr>
-        <c:dLbl>
-          <c:idx val="0"/>
-          <c:tx>
-            <c:rich>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-                <a:spAutoFit/>
-              </a:bodyPr>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr sz="1500" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                    <a:solidFill>
-                      <a:schemeClr val="bg1"/>
-                    </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                    <a:ea typeface="+mn-ea"/>
-                    <a:cs typeface="+mn-cs"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:fld id="{142230AB-E1CA-4ED0-90B8-AE72AFD4AEB8}" type="CELLRANGE">
-                  <a:rPr lang="en-US"/>
-                  <a:pPr>
-                    <a:defRPr sz="1500" b="1">
-                      <a:solidFill>
-                        <a:schemeClr val="bg1"/>
-                      </a:solidFill>
-                    </a:defRPr>
-                  </a:pPr>
-                  <a:t>[CELLRANGE]</a:t>
-                </a:fld>
-                <a:r>
-                  <a:rPr lang="en-US" baseline="0"/>
-                  <a:t>:</a:t>
-                </a:r>
-                <a:fld id="{615B0784-88AA-48A9-AC34-1FDCCF05CDEA}" type="VALUE">
-                  <a:rPr lang="en-US" baseline="0"/>
-                  <a:pPr>
-                    <a:defRPr sz="1500" b="1">
-                      <a:solidFill>
-                        <a:schemeClr val="bg1"/>
-                      </a:solidFill>
-                    </a:defRPr>
-                  </a:pPr>
-                  <a:t>[VALUE]</a:t>
-                </a:fld>
-                <a:endParaRPr lang="en-US" baseline="0"/>
-              </a:p>
-            </c:rich>
-          </c:tx>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-              <a:spAutoFit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="1500" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="bg1"/>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="en-US"/>
-            </a:p>
-          </c:txPr>
-          <c:dLblPos val="inEnd"/>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="1"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-          <c:separator>:</c:separator>
-          <c:extLst>
-            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-              <c15:dlblFieldTable/>
-              <c15:xForSave val="1"/>
-              <c15:showDataLabelsRange val="1"/>
-            </c:ext>
-          </c:extLst>
-        </c:dLbl>
       </c:pivotFmt>
       <c:pivotFmt>
         <c:idx val="3"/>
@@ -6910,97 +7214,6 @@
             </a:contourClr>
           </a:sp3d>
         </c:spPr>
-        <c:dLbl>
-          <c:idx val="0"/>
-          <c:tx>
-            <c:rich>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-                <a:spAutoFit/>
-              </a:bodyPr>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr sz="1500" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                    <a:solidFill>
-                      <a:schemeClr val="bg1"/>
-                    </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                    <a:ea typeface="+mn-ea"/>
-                    <a:cs typeface="+mn-cs"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:fld id="{AA7F3170-2036-408D-832C-FB72263571A2}" type="CELLRANGE">
-                  <a:rPr lang="en-US"/>
-                  <a:pPr>
-                    <a:defRPr sz="1500" b="1">
-                      <a:solidFill>
-                        <a:schemeClr val="bg1"/>
-                      </a:solidFill>
-                    </a:defRPr>
-                  </a:pPr>
-                  <a:t>[CELLRANGE]</a:t>
-                </a:fld>
-                <a:r>
-                  <a:rPr lang="en-US" baseline="0"/>
-                  <a:t>:</a:t>
-                </a:r>
-                <a:fld id="{572EA2C2-0D0D-4C07-8656-CD205868534D}" type="VALUE">
-                  <a:rPr lang="en-US" baseline="0"/>
-                  <a:pPr>
-                    <a:defRPr sz="1500" b="1">
-                      <a:solidFill>
-                        <a:schemeClr val="bg1"/>
-                      </a:solidFill>
-                    </a:defRPr>
-                  </a:pPr>
-                  <a:t>[VALUE]</a:t>
-                </a:fld>
-                <a:endParaRPr lang="en-US" baseline="0"/>
-              </a:p>
-            </c:rich>
-          </c:tx>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-              <a:spAutoFit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="1500" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="bg1"/>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="en-US"/>
-            </a:p>
-          </c:txPr>
-          <c:dLblPos val="inEnd"/>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="1"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-          <c:separator>:</c:separator>
-          <c:extLst>
-            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-              <c15:dlblFieldTable/>
-              <c15:xForSave val="1"/>
-              <c15:showDataLabelsRange val="1"/>
-            </c:ext>
-          </c:extLst>
-        </c:dLbl>
       </c:pivotFmt>
       <c:pivotFmt>
         <c:idx val="4"/>
@@ -7020,97 +7233,6 @@
             </a:contourClr>
           </a:sp3d>
         </c:spPr>
-        <c:dLbl>
-          <c:idx val="0"/>
-          <c:tx>
-            <c:rich>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-                <a:spAutoFit/>
-              </a:bodyPr>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr sz="1500" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                    <a:solidFill>
-                      <a:schemeClr val="bg1"/>
-                    </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                    <a:ea typeface="+mn-ea"/>
-                    <a:cs typeface="+mn-cs"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:fld id="{43DC1A02-CF48-450C-B85B-B47EC20C3EB4}" type="CELLRANGE">
-                  <a:rPr lang="en-US"/>
-                  <a:pPr>
-                    <a:defRPr sz="1500" b="1">
-                      <a:solidFill>
-                        <a:schemeClr val="bg1"/>
-                      </a:solidFill>
-                    </a:defRPr>
-                  </a:pPr>
-                  <a:t>[CELLRANGE]</a:t>
-                </a:fld>
-                <a:r>
-                  <a:rPr lang="en-US" baseline="0"/>
-                  <a:t>:</a:t>
-                </a:r>
-                <a:fld id="{C0E695A4-7EA4-4A6E-AA82-B332F14B842C}" type="VALUE">
-                  <a:rPr lang="en-US" baseline="0"/>
-                  <a:pPr>
-                    <a:defRPr sz="1500" b="1">
-                      <a:solidFill>
-                        <a:schemeClr val="bg1"/>
-                      </a:solidFill>
-                    </a:defRPr>
-                  </a:pPr>
-                  <a:t>[VALUE]</a:t>
-                </a:fld>
-                <a:endParaRPr lang="en-US" baseline="0"/>
-              </a:p>
-            </c:rich>
-          </c:tx>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-              <a:spAutoFit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="1500" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="bg1"/>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="en-US"/>
-            </a:p>
-          </c:txPr>
-          <c:dLblPos val="inEnd"/>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="1"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-          <c:separator>:</c:separator>
-          <c:extLst>
-            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-              <c15:dlblFieldTable/>
-              <c15:xForSave val="1"/>
-              <c15:showDataLabelsRange val="1"/>
-            </c:ext>
-          </c:extLst>
-        </c:dLbl>
       </c:pivotFmt>
       <c:pivotFmt>
         <c:idx val="5"/>
@@ -7130,97 +7252,6 @@
             </a:contourClr>
           </a:sp3d>
         </c:spPr>
-        <c:dLbl>
-          <c:idx val="0"/>
-          <c:tx>
-            <c:rich>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-                <a:spAutoFit/>
-              </a:bodyPr>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr sz="1500" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                    <a:solidFill>
-                      <a:schemeClr val="bg1"/>
-                    </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                    <a:ea typeface="+mn-ea"/>
-                    <a:cs typeface="+mn-cs"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:fld id="{A8D7FA64-D0E7-4918-A38D-21ED88406DAD}" type="CELLRANGE">
-                  <a:rPr lang="en-US"/>
-                  <a:pPr>
-                    <a:defRPr sz="1500" b="1">
-                      <a:solidFill>
-                        <a:schemeClr val="bg1"/>
-                      </a:solidFill>
-                    </a:defRPr>
-                  </a:pPr>
-                  <a:t>[CELLRANGE]</a:t>
-                </a:fld>
-                <a:r>
-                  <a:rPr lang="en-US" baseline="0"/>
-                  <a:t>:</a:t>
-                </a:r>
-                <a:fld id="{4C7F7C53-F7F7-4AF2-ABDB-D31516567DA5}" type="VALUE">
-                  <a:rPr lang="en-US" baseline="0"/>
-                  <a:pPr>
-                    <a:defRPr sz="1500" b="1">
-                      <a:solidFill>
-                        <a:schemeClr val="bg1"/>
-                      </a:solidFill>
-                    </a:defRPr>
-                  </a:pPr>
-                  <a:t>[VALUE]</a:t>
-                </a:fld>
-                <a:endParaRPr lang="en-US" baseline="0"/>
-              </a:p>
-            </c:rich>
-          </c:tx>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-              <a:spAutoFit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="1500" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="bg1"/>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="en-US"/>
-            </a:p>
-          </c:txPr>
-          <c:dLblPos val="inEnd"/>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="1"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-          <c:separator>:</c:separator>
-          <c:extLst>
-            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-              <c15:dlblFieldTable/>
-              <c15:xForSave val="1"/>
-              <c15:showDataLabelsRange val="1"/>
-            </c:ext>
-          </c:extLst>
-        </c:dLbl>
       </c:pivotFmt>
     </c:pivotFmts>
     <c:view3D>
@@ -7419,8 +7450,8 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{B7281AA5-CFE2-4A22-A6FE-06753E3138AF}" type="CELLRANGE">
-                      <a:rPr lang="en-US"/>
+                    <a:fld id="{80A53F31-036F-47F7-9535-481A93ADA2D9}" type="CELLRANGE">
+                      <a:rPr lang="en-US" baseline="0"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
                     </a:fld>
@@ -7428,7 +7459,7 @@
                       <a:rPr lang="en-US" baseline="0"/>
                       <a:t>:</a:t>
                     </a:r>
-                    <a:fld id="{68246D07-8DB1-4D7F-9318-0C774C1DC43B}" type="VALUE">
+                    <a:fld id="{3D1BF7A5-7952-48D6-A5EE-01AF6EDB3A5A}" type="VALUE">
                       <a:rPr lang="en-US" baseline="0"/>
                       <a:pPr/>
                       <a:t>[VALUE]</a:t>
@@ -7461,182 +7492,6 @@
                 </c:ext>
               </c:extLst>
             </c:dLbl>
-            <c:dLbl>
-              <c:idx val="1"/>
-              <c:tx>
-                <c:rich>
-                  <a:bodyPr/>
-                  <a:lstStyle/>
-                  <a:p>
-                    <a:fld id="{142230AB-E1CA-4ED0-90B8-AE72AFD4AEB8}" type="CELLRANGE">
-                      <a:rPr lang="en-US"/>
-                      <a:pPr/>
-                      <a:t>[CELLRANGE]</a:t>
-                    </a:fld>
-                    <a:r>
-                      <a:rPr lang="en-US" baseline="0"/>
-                      <a:t>:</a:t>
-                    </a:r>
-                    <a:fld id="{615B0784-88AA-48A9-AC34-1FDCCF05CDEA}" type="VALUE">
-                      <a:rPr lang="en-US" baseline="0"/>
-                      <a:pPr/>
-                      <a:t>[VALUE]</a:t>
-                    </a:fld>
-                    <a:endParaRPr lang="en-US" baseline="0"/>
-                  </a:p>
-                </c:rich>
-              </c:tx>
-              <c:dLblPos val="inEnd"/>
-              <c:showLegendKey val="0"/>
-              <c:showVal val="1"/>
-              <c:showCatName val="0"/>
-              <c:showSerName val="0"/>
-              <c:showPercent val="0"/>
-              <c:showBubbleSize val="0"/>
-              <c:separator>:</c:separator>
-              <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                  <c15:dlblFieldTable/>
-                  <c15:xForSave val="1"/>
-                  <c15:showDataLabelsRange val="1"/>
-                </c:ext>
-                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000003-15C6-481F-8EDC-2645D999181B}"/>
-                </c:ext>
-              </c:extLst>
-            </c:dLbl>
-            <c:dLbl>
-              <c:idx val="2"/>
-              <c:tx>
-                <c:rich>
-                  <a:bodyPr/>
-                  <a:lstStyle/>
-                  <a:p>
-                    <a:fld id="{AA7F3170-2036-408D-832C-FB72263571A2}" type="CELLRANGE">
-                      <a:rPr lang="en-US"/>
-                      <a:pPr/>
-                      <a:t>[CELLRANGE]</a:t>
-                    </a:fld>
-                    <a:r>
-                      <a:rPr lang="en-US" baseline="0"/>
-                      <a:t>:</a:t>
-                    </a:r>
-                    <a:fld id="{572EA2C2-0D0D-4C07-8656-CD205868534D}" type="VALUE">
-                      <a:rPr lang="en-US" baseline="0"/>
-                      <a:pPr/>
-                      <a:t>[VALUE]</a:t>
-                    </a:fld>
-                    <a:endParaRPr lang="en-US" baseline="0"/>
-                  </a:p>
-                </c:rich>
-              </c:tx>
-              <c:dLblPos val="inEnd"/>
-              <c:showLegendKey val="0"/>
-              <c:showVal val="1"/>
-              <c:showCatName val="0"/>
-              <c:showSerName val="0"/>
-              <c:showPercent val="0"/>
-              <c:showBubbleSize val="0"/>
-              <c:separator>:</c:separator>
-              <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                  <c15:dlblFieldTable/>
-                  <c15:xForSave val="1"/>
-                  <c15:showDataLabelsRange val="1"/>
-                </c:ext>
-                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000005-15C6-481F-8EDC-2645D999181B}"/>
-                </c:ext>
-              </c:extLst>
-            </c:dLbl>
-            <c:dLbl>
-              <c:idx val="3"/>
-              <c:tx>
-                <c:rich>
-                  <a:bodyPr/>
-                  <a:lstStyle/>
-                  <a:p>
-                    <a:fld id="{43DC1A02-CF48-450C-B85B-B47EC20C3EB4}" type="CELLRANGE">
-                      <a:rPr lang="en-US"/>
-                      <a:pPr/>
-                      <a:t>[CELLRANGE]</a:t>
-                    </a:fld>
-                    <a:r>
-                      <a:rPr lang="en-US" baseline="0"/>
-                      <a:t>:</a:t>
-                    </a:r>
-                    <a:fld id="{C0E695A4-7EA4-4A6E-AA82-B332F14B842C}" type="VALUE">
-                      <a:rPr lang="en-US" baseline="0"/>
-                      <a:pPr/>
-                      <a:t>[VALUE]</a:t>
-                    </a:fld>
-                    <a:endParaRPr lang="en-US" baseline="0"/>
-                  </a:p>
-                </c:rich>
-              </c:tx>
-              <c:dLblPos val="inEnd"/>
-              <c:showLegendKey val="0"/>
-              <c:showVal val="1"/>
-              <c:showCatName val="0"/>
-              <c:showSerName val="0"/>
-              <c:showPercent val="0"/>
-              <c:showBubbleSize val="0"/>
-              <c:separator>:</c:separator>
-              <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                  <c15:dlblFieldTable/>
-                  <c15:xForSave val="1"/>
-                  <c15:showDataLabelsRange val="1"/>
-                </c:ext>
-                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000007-15C6-481F-8EDC-2645D999181B}"/>
-                </c:ext>
-              </c:extLst>
-            </c:dLbl>
-            <c:dLbl>
-              <c:idx val="4"/>
-              <c:tx>
-                <c:rich>
-                  <a:bodyPr/>
-                  <a:lstStyle/>
-                  <a:p>
-                    <a:fld id="{A8D7FA64-D0E7-4918-A38D-21ED88406DAD}" type="CELLRANGE">
-                      <a:rPr lang="en-US"/>
-                      <a:pPr/>
-                      <a:t>[CELLRANGE]</a:t>
-                    </a:fld>
-                    <a:r>
-                      <a:rPr lang="en-US" baseline="0"/>
-                      <a:t>:</a:t>
-                    </a:r>
-                    <a:fld id="{4C7F7C53-F7F7-4AF2-ABDB-D31516567DA5}" type="VALUE">
-                      <a:rPr lang="en-US" baseline="0"/>
-                      <a:pPr/>
-                      <a:t>[VALUE]</a:t>
-                    </a:fld>
-                    <a:endParaRPr lang="en-US" baseline="0"/>
-                  </a:p>
-                </c:rich>
-              </c:tx>
-              <c:dLblPos val="inEnd"/>
-              <c:showLegendKey val="0"/>
-              <c:showVal val="1"/>
-              <c:showCatName val="0"/>
-              <c:showSerName val="0"/>
-              <c:showPercent val="0"/>
-              <c:showBubbleSize val="0"/>
-              <c:separator>:</c:separator>
-              <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                  <c15:dlblFieldTable/>
-                  <c15:xForSave val="1"/>
-                  <c15:showDataLabelsRange val="1"/>
-                </c:ext>
-                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000009-15C6-481F-8EDC-2645D999181B}"/>
-                </c:ext>
-              </c:extLst>
-            </c:dLbl>
             <c:spPr>
               <a:noFill/>
               <a:ln>
@@ -7651,9 +7506,12 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="1500" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
-                      <a:schemeClr val="bg1"/>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
                     </a:solidFill>
                     <a:latin typeface="+mn-lt"/>
                     <a:ea typeface="+mn-ea"/>
@@ -7663,33 +7521,14 @@
                 <a:endParaRPr lang="en-US"/>
               </a:p>
             </c:txPr>
-            <c:dLblPos val="inEnd"/>
             <c:showLegendKey val="0"/>
-            <c:showVal val="1"/>
+            <c:showVal val="0"/>
             <c:showCatName val="0"/>
             <c:showSerName val="0"/>
             <c:showPercent val="0"/>
             <c:showBubbleSize val="0"/>
-            <c:separator>:</c:separator>
-            <c:showLeaderLines val="1"/>
-            <c:leaderLines>
-              <c:spPr>
-                <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="35000"/>
-                      <a:lumOff val="65000"/>
-                    </a:schemeClr>
-                  </a:solidFill>
-                  <a:round/>
-                </a:ln>
-                <a:effectLst/>
-              </c:spPr>
-            </c:leaderLines>
             <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:showDataLabelsRange val="1"/>
-              </c:ext>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
             </c:extLst>
           </c:dLbls>
           <c:cat>
@@ -8588,7 +8427,7 @@
                     <a:cs typeface="+mn-cs"/>
                   </a:defRPr>
                 </a:pPr>
-                <a:fld id="{FAA73653-082A-48D9-A35A-AA128EBF2B4D}" type="CELLRANGE">
+                <a:fld id="{8F45C718-3D00-4A60-B737-8C5B033F37D3}" type="CELLRANGE">
                   <a:rPr lang="en-US"/>
                   <a:pPr>
                     <a:defRPr/>
@@ -8599,7 +8438,7 @@
                   <a:rPr lang="en-US" baseline="0"/>
                   <a:t>, </a:t>
                 </a:r>
-                <a:fld id="{52D0750C-37A4-4BE2-A8B2-6D1F5501B655}" type="PERCENTAGE">
+                <a:fld id="{44CE1CA5-C43D-4461-B18E-63CDA9C55642}" type="PERCENTAGE">
                   <a:rPr lang="en-US" baseline="0"/>
                   <a:pPr>
                     <a:defRPr/>
@@ -8707,7 +8546,7 @@
                     <a:cs typeface="+mn-cs"/>
                   </a:defRPr>
                 </a:pPr>
-                <a:fld id="{77BE086E-F7CA-4010-80BF-BA1499C827E4}" type="CELLRANGE">
+                <a:fld id="{387CD0F9-5B13-42CF-8923-C1C6A7A93072}" type="CELLRANGE">
                   <a:rPr lang="en-US"/>
                   <a:pPr>
                     <a:defRPr/>
@@ -8718,7 +8557,7 @@
                   <a:rPr lang="en-US" baseline="0"/>
                   <a:t>, </a:t>
                 </a:r>
-                <a:fld id="{A8D858E8-9378-4471-93D8-043BC51E5B08}" type="PERCENTAGE">
+                <a:fld id="{7A8FD282-CF92-4529-820D-4C527BCE900B}" type="PERCENTAGE">
                   <a:rPr lang="en-US" baseline="0"/>
                   <a:pPr>
                     <a:defRPr/>
@@ -8870,7 +8709,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{FAA73653-082A-48D9-A35A-AA128EBF2B4D}" type="CELLRANGE">
+                    <a:fld id="{8F45C718-3D00-4A60-B737-8C5B033F37D3}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -8879,7 +8718,7 @@
                       <a:rPr lang="en-US" baseline="0"/>
                       <a:t>, </a:t>
                     </a:r>
-                    <a:fld id="{52D0750C-37A4-4BE2-A8B2-6D1F5501B655}" type="PERCENTAGE">
+                    <a:fld id="{44CE1CA5-C43D-4461-B18E-63CDA9C55642}" type="PERCENTAGE">
                       <a:rPr lang="en-US" baseline="0"/>
                       <a:pPr/>
                       <a:t>[PERCENTAGE]</a:t>
@@ -8913,7 +8752,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{77BE086E-F7CA-4010-80BF-BA1499C827E4}" type="CELLRANGE">
+                    <a:fld id="{387CD0F9-5B13-42CF-8923-C1C6A7A93072}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -8922,7 +8761,7 @@
                       <a:rPr lang="en-US" baseline="0"/>
                       <a:t>, </a:t>
                     </a:r>
-                    <a:fld id="{A8D858E8-9378-4471-93D8-043BC51E5B08}" type="PERCENTAGE">
+                    <a:fld id="{7A8FD282-CF92-4529-820D-4C527BCE900B}" type="PERCENTAGE">
                       <a:rPr lang="en-US" baseline="0"/>
                       <a:pPr/>
                       <a:t>[PERCENTAGE]</a:t>
@@ -9257,6 +9096,7 @@
               </a:prstClr>
             </a:outerShdw>
           </a:effectLst>
+          <a:sp3d/>
         </c:spPr>
         <c:marker>
           <c:symbol val="none"/>
@@ -9289,7 +9129,6 @@
               <a:endParaRPr lang="en-US"/>
             </a:p>
           </c:txPr>
-          <c:dLblPos val="inEnd"/>
           <c:showLegendKey val="0"/>
           <c:showVal val="1"/>
           <c:showCatName val="0"/>
@@ -9302,11 +9141,63 @@
         </c:dLbl>
       </c:pivotFmt>
     </c:pivotFmts>
+    <c:view3D>
+      <c:rotX val="15"/>
+      <c:rotY val="20"/>
+      <c:rAngAx val="0"/>
+    </c:view3D>
+    <c:floor>
+      <c:thickness val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+        <a:sp3d/>
+      </c:spPr>
+    </c:floor>
+    <c:sideWall>
+      <c:thickness val="0"/>
+      <c:spPr>
+        <a:solidFill>
+          <a:schemeClr val="bg1"/>
+        </a:solidFill>
+        <a:ln w="25400">
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+        <a:sp3d/>
+      </c:spPr>
+    </c:sideWall>
+    <c:backWall>
+      <c:thickness val="0"/>
+      <c:spPr>
+        <a:solidFill>
+          <a:schemeClr val="bg1"/>
+        </a:solidFill>
+        <a:ln w="25400">
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+        <a:sp3d/>
+      </c:spPr>
+    </c:backWall>
     <c:plotArea>
-      <c:layout/>
-      <c:barChart>
-        <c:barDir val="col"/>
-        <c:grouping val="clustered"/>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.22127600544325479"/>
+          <c:y val="0.13210313681783312"/>
+          <c:w val="0.73335692315203105"/>
+          <c:h val="0.79036300484939359"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:bar3DChart>
+        <c:barDir val="bar"/>
+        <c:grouping val="percentStacked"/>
         <c:varyColors val="0"/>
         <c:ser>
           <c:idx val="0"/>
@@ -9346,6 +9237,7 @@
                 </a:prstClr>
               </a:outerShdw>
             </a:effectLst>
+            <a:sp3d/>
           </c:spPr>
           <c:invertIfNegative val="0"/>
           <c:dLbls>
@@ -9375,7 +9267,6 @@
                 <a:endParaRPr lang="en-US"/>
               </a:p>
             </c:txPr>
-            <c:dLblPos val="inEnd"/>
             <c:showLegendKey val="0"/>
             <c:showVal val="1"/>
             <c:showCatName val="0"/>
@@ -9462,7 +9353,6 @@
           </c:extLst>
         </c:ser>
         <c:dLbls>
-          <c:dLblPos val="inEnd"/>
           <c:showLegendKey val="0"/>
           <c:showVal val="1"/>
           <c:showCatName val="0"/>
@@ -9471,24 +9361,26 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="41"/>
+        <c:shape val="cylinder"/>
         <c:axId val="1925551295"/>
         <c:axId val="1964420639"/>
-      </c:barChart>
+        <c:axId val="0"/>
+      </c:bar3DChart>
       <c:catAx>
         <c:axId val="1925551295"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
         <c:delete val="0"/>
-        <c:axPos val="b"/>
+        <c:axPos val="l"/>
         <c:title>
           <c:tx>
             <c:rich>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:defRPr sz="1500" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
                       <a:schemeClr val="dk1">
                         <a:lumMod val="65000"/>
@@ -9501,14 +9393,9 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:rPr lang="en-US"/>
-                  <a:t>Average</a:t>
+                  <a:rPr lang="en-US" sz="1500"/>
+                  <a:t>State</a:t>
                 </a:r>
-                <a:r>
-                  <a:rPr lang="en-US" baseline="0"/>
-                  <a:t> Marks</a:t>
-                </a:r>
-                <a:endParaRPr lang="en-US"/>
               </a:p>
             </c:rich>
           </c:tx>
@@ -9516,8 +9403,8 @@
             <c:manualLayout>
               <c:xMode val="edge"/>
               <c:yMode val="edge"/>
-              <c:x val="0.47484022793083486"/>
-              <c:y val="0.83460743011232241"/>
+              <c:x val="2.6210299595328109E-2"/>
+              <c:y val="0.45159261370066422"/>
             </c:manualLayout>
           </c:layout>
           <c:overlay val="0"/>
@@ -9529,11 +9416,11 @@
             <a:effectLst/>
           </c:spPr>
           <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
             <a:lstStyle/>
             <a:p>
               <a:pPr>
-                <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:defRPr sz="1500" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                   <a:solidFill>
                     <a:schemeClr val="dk1">
                       <a:lumMod val="65000"/>
@@ -9565,7 +9452,7 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
                   <a:schemeClr val="dk1">
                     <a:lumMod val="65000"/>
@@ -9594,15 +9481,15 @@
           <c:orientation val="minMax"/>
         </c:scaling>
         <c:delete val="1"/>
-        <c:axPos val="l"/>
+        <c:axPos val="b"/>
         <c:title>
           <c:tx>
             <c:rich>
-              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:defRPr sz="1500" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
                       <a:schemeClr val="dk1">
                         <a:lumMod val="65000"/>
@@ -9615,12 +9502,25 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:rPr lang="en-US"/>
-                  <a:t>Stae</a:t>
+                  <a:rPr lang="en-US" sz="1500"/>
+                  <a:t>Average</a:t>
                 </a:r>
+                <a:r>
+                  <a:rPr lang="en-US" sz="1500" baseline="0"/>
+                  <a:t> Marks</a:t>
+                </a:r>
+                <a:endParaRPr lang="en-US" sz="1500"/>
               </a:p>
             </c:rich>
           </c:tx>
+          <c:layout>
+            <c:manualLayout>
+              <c:xMode val="edge"/>
+              <c:yMode val="edge"/>
+              <c:x val="0.43083317638761021"/>
+              <c:y val="0.86836117610813257"/>
+            </c:manualLayout>
+          </c:layout>
           <c:overlay val="0"/>
           <c:spPr>
             <a:noFill/>
@@ -9630,11 +9530,11 @@
             <a:effectLst/>
           </c:spPr>
           <c:txPr>
-            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
             <a:lstStyle/>
             <a:p>
               <a:pPr>
-                <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:defRPr sz="1500" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                   <a:solidFill>
                     <a:schemeClr val="dk1">
                       <a:lumMod val="65000"/>
@@ -9650,7 +9550,7 @@
             </a:p>
           </c:txPr>
         </c:title>
-        <c:numFmt formatCode="0.000" sourceLinked="1"/>
+        <c:numFmt formatCode="0%" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -9659,10 +9559,8 @@
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:spPr>
-        <a:solidFill>
-          <a:schemeClr val="bg1"/>
-        </a:solidFill>
-        <a:ln w="25400">
+        <a:noFill/>
+        <a:ln>
           <a:noFill/>
         </a:ln>
         <a:effectLst/>
@@ -9715,7 +9613,6 @@
         <c14:dropZoneFilter val="1"/>
         <c14:dropZoneCategories val="1"/>
         <c14:dropZoneData val="1"/>
-        <c14:dropZonesVisible val="1"/>
       </c14:pivotOptions>
     </c:ext>
     <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{E28EC0CA-F0BB-4C9C-879D-F8772B89E7AC}">
@@ -10926,6 +10823,46 @@
 </file>
 
 <file path=xl/charts/colors11.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors12.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
   <a:schemeClr val="accent2"/>
@@ -12495,6 +12432,525 @@
       <cs:styleClr val="auto"/>
     </cs:lnRef>
     <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style12.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="251">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="25400">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
@@ -17176,6 +17632,10 @@
 </cs:chartStyle>
 </file>
 
+<file path=xl/ctrlProps/ctrlProp1.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Spin" dx="22" fmlaLink="$F$2" max="30000" page="10" val="200"/>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
@@ -17575,6 +18035,211 @@
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>400050</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>23812</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>95250</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>100012</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2C9280C9-1794-4CCB-ABB7-417EB7F82025}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor>
+        <xdr:from>
+          <xdr:col>6</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>1</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>7</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>2</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="7171" name="Spinner 3" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s7171"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{214673AE-1D5D-4B8B-9776-8DA1E3EDE0B8}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="9525">
+              <a:miter lim="800000"/>
+              <a:headEnd/>
+              <a:tailEnd/>
+            </a:ln>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>495301</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>47625</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>9525</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>142874</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="$F$2">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="6" name="TextBox 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8FB91746-FA95-4D05-96E6-D4120FA88DE7}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5981701" y="1762125"/>
+          <a:ext cx="733424" cy="476249"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525" cmpd="sng">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:fld id="{6E0E4F28-749F-460D-BCE1-28DE9BF153C6}" type="TxLink">
+            <a:rPr lang="en-US" sz="2800" b="1" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Calibri"/>
+              <a:cs typeface="Calibri"/>
+            </a:rPr>
+            <a:t>200</a:t>
+          </a:fld>
+          <a:endParaRPr lang="en-US" sz="2800" b="1"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<c:userShapes xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <cdr:relSizeAnchor xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing">
+    <cdr:from>
+      <cdr:x>0.28542</cdr:x>
+      <cdr:y>0.53646</cdr:y>
+    </cdr:from>
+    <cdr:to>
+      <cdr:x>0.725</cdr:x>
+      <cdr:y>0.67882</cdr:y>
+    </cdr:to>
+    <cdr:sp macro="" textlink="">
+      <cdr:nvSpPr>
+        <cdr:cNvPr id="2" name="TextBox 1">
+          <a:extLst xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9A36B3D0-AF73-42DB-92D6-72C0685D9908}"/>
+            </a:ext>
+          </a:extLst>
+        </cdr:cNvPr>
+        <cdr:cNvSpPr txBox="1"/>
+      </cdr:nvSpPr>
+      <cdr:spPr>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:off x="1304925" y="1471613"/>
+          <a:ext cx="2009775" cy="390525"/>
+        </a:xfrm>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </cdr:spPr>
+      <cdr:txBody>
+        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" vertOverflow="clip" wrap="square" rtlCol="0"/>
+        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:endParaRPr lang="en-US" sz="1100"/>
+        </a:p>
+      </cdr:txBody>
+    </cdr:sp>
+  </cdr:relSizeAnchor>
+</c:userShapes>
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -33983,11 +34648,11 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{9B6BDE34-F046-4EBD-A029-7B13681B5329}" name="PivotTable3" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="K3:M16" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{20A7135E-67C0-4B3D-A7BF-387C811BC08A}" name="PivotTable2" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="F3:I10" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="15">
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField axis="axisCol" showAll="0">
       <items count="3">
         <item x="1"/>
         <item x="0"/>
@@ -34016,476 +34681,22 @@
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="6">
+        <item x="0"/>
+        <item x="2"/>
+        <item x="1"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
     <pivotField multipleItemSelectionAllowed="1" showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="5">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="3"/>
-        <item x="2"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="7">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="12">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-  </pivotFields>
-  <rowFields count="2">
-    <field x="12"/>
-    <field x="1"/>
-  </rowFields>
-  <rowItems count="13">
-    <i>
-      <x/>
-    </i>
-    <i r="1">
-      <x/>
-    </i>
-    <i r="1">
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i r="1">
-      <x/>
-    </i>
-    <i r="1">
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i r="1">
-      <x/>
-    </i>
-    <i r="1">
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i r="1">
-      <x/>
-    </i>
-    <i r="1">
-      <x v="1"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colFields count="1">
-    <field x="-2"/>
-  </colFields>
-  <colItems count="2">
-    <i>
-      <x/>
-    </i>
-    <i i="1">
-      <x v="1"/>
-    </i>
-  </colItems>
-  <dataFields count="2">
-    <dataField name="Max of Total_Marks_720" fld="11" subtotal="max" baseField="11" baseItem="0"/>
-    <dataField name="Min of Total_Marks_720" fld="11" subtotal="min" baseField="11" baseItem="0"/>
-  </dataFields>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable10.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{93AFE857-C7B9-4F75-98D3-04F9FD33CE41}" name="PivotTable7" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1">
-  <location ref="F24:G31" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="15">
     <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="14" showAll="0">
-      <items count="15">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="12"/>
-        <item x="13"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="7">
-        <item x="1"/>
-        <item x="3"/>
-        <item x="0"/>
-        <item x="2"/>
-        <item x="5"/>
-        <item x="4"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0">
-      <items count="7">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="12">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="5"/>
-  </rowFields>
-  <rowItems count="7">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i>
-      <x v="5"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Average of Total_Marks_720" fld="11" subtotal="average" baseField="1" baseItem="1" numFmtId="164"/>
-  </dataFields>
-  <formats count="6">
-    <format dxfId="11">
-      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="10">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="9">
-      <pivotArea field="5" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
-    </format>
-    <format dxfId="8">
-      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
-        <references count="1">
-          <reference field="5" count="0"/>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="7">
-      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="6">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
-    </format>
-  </formats>
-  <chartFormats count="1">
-    <chartFormat chart="0" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable11.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{685B6D20-18B4-41AB-B9DA-B5E400E24AC6}" name="PivotTable18" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1">
-  <location ref="X23:Y34" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="15">
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="14" showAll="0">
-      <items count="15">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="12"/>
-        <item x="13"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="11">
-        <item x="9"/>
-        <item x="2"/>
-        <item x="0"/>
-        <item x="1"/>
-        <item x="8"/>
-        <item x="6"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="7"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0">
-      <items count="7">
-        <item sd="0" x="0"/>
-        <item sd="0" x="1"/>
-        <item sd="0" x="2"/>
-        <item sd="0" x="3"/>
-        <item sd="0" x="4"/>
-        <item sd="0" x="5"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="12">
-        <item sd="0" x="0"/>
-        <item sd="0" x="1"/>
-        <item sd="0" x="2"/>
-        <item sd="0" x="3"/>
-        <item sd="0" x="4"/>
-        <item sd="0" x="5"/>
-        <item sd="0" x="6"/>
-        <item sd="0" x="7"/>
-        <item sd="0" x="8"/>
-        <item sd="0" x="9"/>
-        <item sd="0" x="10"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="3"/>
-  </rowFields>
-  <rowItems count="11">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i>
-      <x v="5"/>
-    </i>
-    <i>
-      <x v="6"/>
-    </i>
-    <i>
-      <x v="7"/>
-    </i>
-    <i>
-      <x v="8"/>
-    </i>
-    <i>
-      <x v="9"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Average of Total_Marks_720" fld="11" subtotal="average" baseField="1" baseItem="1" numFmtId="164"/>
-  </dataFields>
-  <formats count="6">
-    <format dxfId="17">
-      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="16">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="15">
-      <pivotArea field="3" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
-    </format>
-    <format dxfId="14">
-      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
-        <references count="1">
-          <reference field="3" count="0"/>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="13">
-      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="12">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
-    </format>
-  </formats>
-  <chartFormats count="1">
-    <chartFormat chart="0" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable12.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{EE754676-FE8C-485A-9104-879DD87B02BF}" name="PivotTable10" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="9">
-  <location ref="S24:T29" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="15">
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="14" showAll="0">
-      <items count="15">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="12"/>
-        <item x="13"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
+    <pivotField axis="axisPage" showAll="0">
       <items count="5">
         <item x="0"/>
         <item x="1"/>
@@ -34523,300 +34734,9 @@
     </pivotField>
   </pivotFields>
   <rowFields count="1">
-    <field x="12"/>
+    <field x="6"/>
   </rowFields>
-  <rowItems count="5">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Average of Total_Marks_720" fld="11" subtotal="average" baseField="1" baseItem="1" numFmtId="164"/>
-  </dataFields>
-  <formats count="6">
-    <format dxfId="23">
-      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="22">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="21">
-      <pivotArea field="12" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
-    </format>
-    <format dxfId="20">
-      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
-        <references count="1">
-          <reference field="12" count="0"/>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="19">
-      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="18">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
-    </format>
-  </formats>
-  <chartFormats count="1">
-    <chartFormat chart="8" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable13.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{7477CAE7-3D84-4979-A079-F219CD7107CD}" name="PivotTable6" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="13">
-  <location ref="B24:C27" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="15">
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="3">
-        <item x="1"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField numFmtId="14" showAll="0">
-      <items count="15">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="12"/>
-        <item x="13"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0">
-      <items count="7">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="12">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="1"/>
-  </rowFields>
-  <rowItems count="3">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Average of Total_Marks_720" fld="11" subtotal="average" baseField="1" baseItem="1"/>
-  </dataFields>
-  <chartFormats count="3">
-    <chartFormat chart="12" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="12" format="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="1" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="12" format="2">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="1" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable14.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{EA245FB0-3DE8-46C9-A0E5-872B68676623}" name="PivotTable5" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="R2:S18" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="15">
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="14" showAll="0">
-      <items count="15">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="12"/>
-        <item x="13"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="16">
-        <item x="3"/>
-        <item x="6"/>
-        <item x="5"/>
-        <item x="2"/>
-        <item x="13"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="7"/>
-        <item x="12"/>
-        <item x="0"/>
-        <item x="4"/>
-        <item x="8"/>
-        <item x="14"/>
-        <item x="1"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0">
-      <items count="7">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="12">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="4"/>
-  </rowFields>
-  <rowItems count="16">
+  <rowItems count="6">
     <i>
       <x/>
     </i>
@@ -34832,45 +34752,29 @@
     <i>
       <x v="4"/>
     </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="1"/>
+  </colFields>
+  <colItems count="3">
     <i>
-      <x v="5"/>
+      <x/>
     </i>
     <i>
-      <x v="6"/>
-    </i>
-    <i>
-      <x v="7"/>
-    </i>
-    <i>
-      <x v="8"/>
-    </i>
-    <i>
-      <x v="9"/>
-    </i>
-    <i>
-      <x v="10"/>
-    </i>
-    <i>
-      <x v="11"/>
-    </i>
-    <i>
-      <x v="12"/>
-    </i>
-    <i>
-      <x v="13"/>
-    </i>
-    <i>
-      <x v="14"/>
+      <x v="1"/>
     </i>
     <i t="grand">
       <x/>
     </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
   </colItems>
+  <pageFields count="1">
+    <pageField fld="12" item="0" hier="-1"/>
+  </pageFields>
   <dataFields count="1">
-    <dataField name="Count of Total_Marks_720" fld="11" subtotal="count" baseField="4" baseItem="0"/>
+    <dataField name="Count of Seat_No" fld="0" subtotal="count" baseField="0" baseItem="0"/>
   </dataFields>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
   <extLst>
@@ -34884,8 +34788,8 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable15.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{A8AC0511-1550-4DE4-9EF4-98BFCD395BCB}" name="PivotTable19" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="25">
+<file path=xl/pivotTables/pivotTable10.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{A8AC0511-1550-4DE4-9EF4-98BFCD395BCB}" name="PivotTable19" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="25">
   <location ref="U2:V13" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="15">
     <pivotField showAll="0"/>
@@ -35028,9 +34932,9 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable16.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{203FA7CD-B653-4584-A13E-B7ABE5CAC113}" name="PivotTable9" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="20">
-  <location ref="N24:O29" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+<file path=xl/pivotTables/pivotTable11.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{93AFE857-C7B9-4F75-98D3-04F9FD33CE41}" name="PivotTable7" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1">
+  <location ref="F24:G31" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="15">
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
@@ -35055,17 +34959,19 @@
     </pivotField>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
     <pivotField axis="axisRow" showAll="0">
-      <items count="5">
+      <items count="7">
+        <item x="1"/>
+        <item x="3"/>
         <item x="0"/>
         <item x="2"/>
-        <item x="3"/>
-        <item x="1"/>
+        <item x="5"/>
+        <item x="4"/>
         <item t="default"/>
       </items>
     </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
@@ -35100,9 +35006,9 @@
     </pivotField>
   </pivotFields>
   <rowFields count="1">
-    <field x="7"/>
+    <field x="5"/>
   </rowFields>
-  <rowItems count="5">
+  <rowItems count="7">
     <i>
       <x/>
     </i>
@@ -35115,6 +35021,12 @@
     <i>
       <x v="3"/>
     </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
     <i t="grand">
       <x/>
     </i>
@@ -35126,31 +35038,31 @@
     <dataField name="Average of Total_Marks_720" fld="11" subtotal="average" baseField="1" baseItem="1" numFmtId="164"/>
   </dataFields>
   <formats count="6">
-    <format dxfId="29">
+    <format dxfId="17">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="28">
+    <format dxfId="16">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="27">
-      <pivotArea field="7" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
+    <format dxfId="15">
+      <pivotArea field="5" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="26">
+    <format dxfId="14">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
-          <reference field="7" count="0"/>
+          <reference field="5" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="25">
+    <format dxfId="13">
       <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="24">
+    <format dxfId="12">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
   </formats>
   <chartFormats count="1">
-    <chartFormat chart="19" format="0" series="1">
+    <chartFormat chart="0" format="0" series="1">
       <pivotArea type="data" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1" selected="0">
@@ -35172,458 +35084,8 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{20A7135E-67C0-4B3D-A7BF-387C811BC08A}" name="PivotTable2" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="F3:I10" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
-  <pivotFields count="15">
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField axis="axisCol" showAll="0">
-      <items count="3">
-        <item x="1"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField numFmtId="14" showAll="0">
-      <items count="15">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="12"/>
-        <item x="13"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="6">
-        <item x="0"/>
-        <item x="2"/>
-        <item x="1"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField multipleItemSelectionAllowed="1" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisPage" showAll="0">
-      <items count="5">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="3"/>
-        <item x="2"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="7">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="12">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="6"/>
-  </rowFields>
-  <rowItems count="6">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colFields count="1">
-    <field x="1"/>
-  </colFields>
-  <colItems count="3">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </colItems>
-  <pageFields count="1">
-    <pageField fld="12" item="0" hier="-1"/>
-  </pageFields>
-  <dataFields count="1">
-    <dataField name="Count of Seat_No" fld="0" subtotal="count" baseField="0" baseItem="0"/>
-  </dataFields>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{B1D71027-9B70-4980-AC08-7AC88083601C}" name="PivotTable1" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="B3:C19" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
-  <pivotFields count="15">
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="14" showAll="0">
-      <items count="15">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="12"/>
-        <item x="13"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="16">
-        <item x="3"/>
-        <item x="6"/>
-        <item x="5"/>
-        <item x="2"/>
-        <item x="13"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="7"/>
-        <item x="12"/>
-        <item x="0"/>
-        <item x="4"/>
-        <item x="8"/>
-        <item x="14"/>
-        <item x="1"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisPage" multipleItemSelectionAllowed="1" showAll="0">
-      <items count="5">
-        <item x="0"/>
-        <item h="1" x="2"/>
-        <item h="1" x="3"/>
-        <item h="1" x="1"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0">
-      <items count="7">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="12">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="4"/>
-  </rowFields>
-  <rowItems count="16">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i>
-      <x v="5"/>
-    </i>
-    <i>
-      <x v="6"/>
-    </i>
-    <i>
-      <x v="7"/>
-    </i>
-    <i>
-      <x v="8"/>
-    </i>
-    <i>
-      <x v="9"/>
-    </i>
-    <i>
-      <x v="10"/>
-    </i>
-    <i>
-      <x v="11"/>
-    </i>
-    <i>
-      <x v="12"/>
-    </i>
-    <i>
-      <x v="13"/>
-    </i>
-    <i>
-      <x v="14"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <pageFields count="1">
-    <pageField fld="7" hier="-1"/>
-  </pageFields>
-  <dataFields count="1">
-    <dataField name="Average of Total_Marks_720" fld="11" subtotal="average" baseField="3" baseItem="0"/>
-  </dataFields>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{981B301C-54BD-4283-904B-4C00DBBF88AE}" name="PivotTable4" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="O4:R10" firstHeaderRow="0" firstDataRow="1" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
-  <pivotFields count="15">
-    <pivotField showAll="0"/>
-    <pivotField axis="axisPage" showAll="0">
-      <items count="3">
-        <item x="1"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField numFmtId="14" showAll="0">
-      <items count="15">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="12"/>
-        <item x="13"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="7">
-        <item x="1"/>
-        <item x="3"/>
-        <item x="0"/>
-        <item x="2"/>
-        <item x="5"/>
-        <item x="4"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField multipleItemSelectionAllowed="1" showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisPage" multipleItemSelectionAllowed="1" showAll="0">
-      <items count="5">
-        <item h="1" x="0"/>
-        <item h="1" x="1"/>
-        <item x="3"/>
-        <item x="2"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="7">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="12">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="5"/>
-  </rowFields>
-  <rowItems count="6">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i>
-      <x v="5"/>
-    </i>
-  </rowItems>
-  <colFields count="1">
-    <field x="-2"/>
-  </colFields>
-  <colItems count="3">
-    <i>
-      <x/>
-    </i>
-    <i i="1">
-      <x v="1"/>
-    </i>
-    <i i="2">
-      <x v="2"/>
-    </i>
-  </colItems>
-  <pageFields count="2">
-    <pageField fld="1" item="1" hier="-1"/>
-    <pageField fld="12" hier="-1"/>
-  </pageFields>
-  <dataFields count="3">
-    <dataField name="Max of Biology_Marks_360" fld="10" subtotal="max" baseField="4" baseItem="0"/>
-    <dataField name="Max of Physics_Marks_180" fld="8" subtotal="max" baseField="4" baseItem="0"/>
-    <dataField name="Max of Chemistry_Marks_180" fld="9" subtotal="max" baseField="4" baseItem="0"/>
-  </dataFields>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{1E1706AB-0ECD-403F-967D-9EFFC071F1B9}" name="PivotTable4" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="5">
+<file path=xl/pivotTables/pivotTable12.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{1E1706AB-0ECD-403F-967D-9EFFC071F1B9}" name="PivotTable4" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="5">
   <location ref="N2:O8" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="15">
     <pivotField showAll="0"/>
@@ -35806,8 +35268,8 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable6.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{FED7A017-AF86-497F-B51C-E14CF94CBD94}" name="PivotTable3" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="27">
+<file path=xl/pivotTables/pivotTable13.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{FED7A017-AF86-497F-B51C-E14CF94CBD94}" name="PivotTable3" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="27">
   <location ref="J2:K7" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="15">
     <pivotField showAll="0"/>
@@ -35935,8 +35397,320 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable7.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{1DC45F1A-B387-4E28-A9F7-EA00F4551286}" name="PivotTable2" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="46">
+<file path=xl/pivotTables/pivotTable14.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{203FA7CD-B653-4584-A13E-B7ABE5CAC113}" name="PivotTable9" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="20">
+  <location ref="N24:O29" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="15">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="14" showAll="0">
+      <items count="15">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="5">
+        <item x="0"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="7">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="12">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="7"/>
+  </rowFields>
+  <rowItems count="5">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Average of Total_Marks_720" fld="11" subtotal="average" baseField="1" baseItem="1" numFmtId="164"/>
+  </dataFields>
+  <formats count="6">
+    <format dxfId="23">
+      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="22">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="21">
+      <pivotArea field="7" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
+    </format>
+    <format dxfId="20">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="1">
+          <reference field="7" count="0"/>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="19">
+      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="18">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
+    </format>
+  </formats>
+  <chartFormats count="1">
+    <chartFormat chart="19" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable15.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{685B6D20-18B4-41AB-B9DA-B5E400E24AC6}" name="PivotTable18" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1">
+  <location ref="X23:Y34" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="15">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="14" showAll="0">
+      <items count="15">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="11">
+        <item x="9"/>
+        <item x="2"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="8"/>
+        <item x="6"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="7"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="7">
+        <item sd="0" x="0"/>
+        <item sd="0" x="1"/>
+        <item sd="0" x="2"/>
+        <item sd="0" x="3"/>
+        <item sd="0" x="4"/>
+        <item sd="0" x="5"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="12">
+        <item sd="0" x="0"/>
+        <item sd="0" x="1"/>
+        <item sd="0" x="2"/>
+        <item sd="0" x="3"/>
+        <item sd="0" x="4"/>
+        <item sd="0" x="5"/>
+        <item sd="0" x="6"/>
+        <item sd="0" x="7"/>
+        <item sd="0" x="8"/>
+        <item sd="0" x="9"/>
+        <item sd="0" x="10"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="3"/>
+  </rowFields>
+  <rowItems count="11">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i>
+      <x v="7"/>
+    </i>
+    <i>
+      <x v="8"/>
+    </i>
+    <i>
+      <x v="9"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Average of Total_Marks_720" fld="11" subtotal="average" baseField="1" baseItem="1" numFmtId="164"/>
+  </dataFields>
+  <formats count="6">
+    <format dxfId="29">
+      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="28">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="27">
+      <pivotArea field="3" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
+    </format>
+    <format dxfId="26">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="1">
+          <reference field="3" count="0"/>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="25">
+      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="24">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
+    </format>
+  </formats>
+  <chartFormats count="1">
+    <chartFormat chart="0" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable16.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{1DC45F1A-B387-4E28-A9F7-EA00F4551286}" name="PivotTable2" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="46">
   <location ref="F2:G9" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="15">
     <pivotField showAll="0"/>
@@ -36063,8 +35837,746 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable8.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{DEFDB440-EFF4-44A0-845D-91489872616B}" name="PivotTable8" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1">
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{B1D71027-9B70-4980-AC08-7AC88083601C}" name="PivotTable1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="B3:C19" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
+  <pivotFields count="15">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="14" showAll="0">
+      <items count="15">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="16">
+        <item x="3"/>
+        <item x="6"/>
+        <item x="5"/>
+        <item x="2"/>
+        <item x="13"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="7"/>
+        <item x="12"/>
+        <item x="0"/>
+        <item x="4"/>
+        <item x="8"/>
+        <item x="14"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisPage" multipleItemSelectionAllowed="1" showAll="0">
+      <items count="5">
+        <item x="0"/>
+        <item h="1" x="2"/>
+        <item h="1" x="3"/>
+        <item h="1" x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="7">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="12">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="4"/>
+  </rowFields>
+  <rowItems count="16">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i>
+      <x v="7"/>
+    </i>
+    <i>
+      <x v="8"/>
+    </i>
+    <i>
+      <x v="9"/>
+    </i>
+    <i>
+      <x v="10"/>
+    </i>
+    <i>
+      <x v="11"/>
+    </i>
+    <i>
+      <x v="12"/>
+    </i>
+    <i>
+      <x v="13"/>
+    </i>
+    <i>
+      <x v="14"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <pageFields count="1">
+    <pageField fld="7" hier="-1"/>
+  </pageFields>
+  <dataFields count="1">
+    <dataField name="Average of Total_Marks_720" fld="11" subtotal="average" baseField="3" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{981B301C-54BD-4283-904B-4C00DBBF88AE}" name="PivotTable4" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="O4:R10" firstHeaderRow="0" firstDataRow="1" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
+  <pivotFields count="15">
+    <pivotField showAll="0"/>
+    <pivotField axis="axisPage" showAll="0">
+      <items count="3">
+        <item x="1"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField numFmtId="14" showAll="0">
+      <items count="15">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="7">
+        <item x="1"/>
+        <item x="3"/>
+        <item x="0"/>
+        <item x="2"/>
+        <item x="5"/>
+        <item x="4"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField multipleItemSelectionAllowed="1" showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisPage" multipleItemSelectionAllowed="1" showAll="0">
+      <items count="5">
+        <item h="1" x="0"/>
+        <item h="1" x="1"/>
+        <item x="3"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="7">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="12">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="5"/>
+  </rowFields>
+  <rowItems count="6">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="-2"/>
+  </colFields>
+  <colItems count="3">
+    <i>
+      <x/>
+    </i>
+    <i i="1">
+      <x v="1"/>
+    </i>
+    <i i="2">
+      <x v="2"/>
+    </i>
+  </colItems>
+  <pageFields count="2">
+    <pageField fld="1" item="1" hier="-1"/>
+    <pageField fld="12" hier="-1"/>
+  </pageFields>
+  <dataFields count="3">
+    <dataField name="Max of Biology_Marks_360" fld="10" subtotal="max" baseField="4" baseItem="0"/>
+    <dataField name="Max of Physics_Marks_180" fld="8" subtotal="max" baseField="4" baseItem="0"/>
+    <dataField name="Max of Chemistry_Marks_180" fld="9" subtotal="max" baseField="4" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{9B6BDE34-F046-4EBD-A029-7B13681B5329}" name="PivotTable3" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="K3:M16" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="15">
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="3">
+        <item x="1"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField numFmtId="14" showAll="0">
+      <items count="15">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField multipleItemSelectionAllowed="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="5">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="3"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="7">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="12">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowFields count="2">
+    <field x="12"/>
+    <field x="1"/>
+  </rowFields>
+  <rowItems count="13">
+    <i>
+      <x/>
+    </i>
+    <i r="1">
+      <x/>
+    </i>
+    <i r="1">
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i r="1">
+      <x/>
+    </i>
+    <i r="1">
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i r="1">
+      <x/>
+    </i>
+    <i r="1">
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i r="1">
+      <x/>
+    </i>
+    <i r="1">
+      <x v="1"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="-2"/>
+  </colFields>
+  <colItems count="2">
+    <i>
+      <x/>
+    </i>
+    <i i="1">
+      <x v="1"/>
+    </i>
+  </colItems>
+  <dataFields count="2">
+    <dataField name="Max of Total_Marks_720" fld="11" subtotal="max" baseField="11" baseItem="0"/>
+    <dataField name="Min of Total_Marks_720" fld="11" subtotal="min" baseField="11" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{EE754676-FE8C-485A-9104-879DD87B02BF}" name="PivotTable10" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="9">
+  <location ref="S24:T29" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="15">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="14" showAll="0">
+      <items count="15">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="5">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="3"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="7">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="12">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="12"/>
+  </rowFields>
+  <rowItems count="5">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Average of Total_Marks_720" fld="11" subtotal="average" baseField="1" baseItem="1" numFmtId="164"/>
+  </dataFields>
+  <formats count="6">
+    <format dxfId="5">
+      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="4">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="3">
+      <pivotArea field="12" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
+    </format>
+    <format dxfId="2">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="1">
+          <reference field="12" count="0"/>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="1">
+      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="0">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
+    </format>
+  </formats>
+  <chartFormats count="1">
+    <chartFormat chart="8" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable6.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{7477CAE7-3D84-4979-A079-F219CD7107CD}" name="PivotTable6" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="13">
+  <location ref="B24:C27" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="15">
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="3">
+        <item x="1"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField numFmtId="14" showAll="0">
+      <items count="15">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="7">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="12">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="1"/>
+  </rowFields>
+  <rowItems count="3">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Average of Total_Marks_720" fld="11" subtotal="average" baseField="1" baseItem="1"/>
+  </dataFields>
+  <chartFormats count="3">
+    <chartFormat chart="12" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="12" format="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="12" format="2">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable7.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{DEFDB440-EFF4-44A0-845D-91489872616B}" name="PivotTable8" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1">
   <location ref="J24:K30" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="15">
     <pivotField showAll="0"/>
@@ -36165,26 +36677,26 @@
     <dataField name="Average of Total_Marks_720" fld="11" subtotal="average" baseField="1" baseItem="1" numFmtId="164"/>
   </dataFields>
   <formats count="6">
-    <format dxfId="5">
+    <format dxfId="11">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="4">
+    <format dxfId="10">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="3">
+    <format dxfId="9">
       <pivotArea field="6" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="2">
+    <format dxfId="8">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="6" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="1">
+    <format dxfId="7">
       <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="0">
+    <format dxfId="6">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
   </formats>
@@ -36211,8 +36723,161 @@
 </pivotTableDefinition>
 </file>
 
+<file path=xl/pivotTables/pivotTable8.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{EA245FB0-3DE8-46C9-A0E5-872B68676623}" name="PivotTable5" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="R2:S18" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="15">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="14" showAll="0">
+      <items count="15">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="16">
+        <item x="3"/>
+        <item x="6"/>
+        <item x="5"/>
+        <item x="2"/>
+        <item x="13"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="7"/>
+        <item x="12"/>
+        <item x="0"/>
+        <item x="4"/>
+        <item x="8"/>
+        <item x="14"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="7">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="12">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="4"/>
+  </rowFields>
+  <rowItems count="16">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i>
+      <x v="7"/>
+    </i>
+    <i>
+      <x v="8"/>
+    </i>
+    <i>
+      <x v="9"/>
+    </i>
+    <i>
+      <x v="10"/>
+    </i>
+    <i>
+      <x v="11"/>
+    </i>
+    <i>
+      <x v="12"/>
+    </i>
+    <i>
+      <x v="13"/>
+    </i>
+    <i>
+      <x v="14"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Count of Total_Marks_720" fld="11" subtotal="count" baseField="4" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
 <file path=xl/pivotTables/pivotTable9.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{22F46C32-CCB7-4722-8A2F-97FF058ACFAE}" name="PivotTable1" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="11">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{22F46C32-CCB7-4722-8A2F-97FF058ACFAE}" name="PivotTable1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="11">
   <location ref="B2:C5" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="15">
     <pivotField showAll="0"/>
@@ -36679,6 +37344,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:M1001"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -46955,7 +47621,7 @@
       </c>
       <c r="D245" s="8">
         <f ca="1">ROUND(YEARFRAC(NEET[[#This Row],[Date_of_Birth]],TODAY()),0)</f>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E245" t="s">
         <v>36</v>
@@ -60899,7 +61565,7 @@
       </c>
       <c r="D577" s="8">
         <f ca="1">ROUND(YEARFRAC(NEET[[#This Row],[Date_of_Birth]],TODAY()),0)</f>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E577" t="s">
         <v>27</v>
@@ -78747,6 +79413,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{71C92FA7-0000-4796-9294-7AD94AC11791}">
+  <sheetPr codeName="Sheet3"/>
   <dimension ref="B2:L20"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -79222,6 +79889,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E91137E5-4F50-406D-9620-CC0D009DA4E9}">
+  <sheetPr codeName="Sheet4"/>
   <dimension ref="B1:FG19"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -80998,6 +81666,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{134C085B-F136-4A27-A28A-A70038132F83}">
+  <sheetPr codeName="Sheet5"/>
   <dimension ref="B2:P21"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -81379,7 +82048,7 @@
       </c>
       <c r="M14">
         <f ca="1">AVERAGEIFS(NEET[Total_Marks_720],NEET[Age of Student],Analysis!L14,NEET[Attempt_No],Analysis!$M$5)</f>
-        <v>399.92857142857144</v>
+        <v>402.74074074074076</v>
       </c>
     </row>
     <row r="15" spans="2:16" x14ac:dyDescent="0.25">
@@ -81403,7 +82072,7 @@
       </c>
       <c r="M15">
         <f ca="1">AVERAGEIFS(NEET[Total_Marks_720],NEET[Age of Student],Analysis!L15,NEET[Attempt_No],Analysis!$M$5)</f>
-        <v>422.61904761904759</v>
+        <v>416</v>
       </c>
     </row>
     <row r="16" spans="2:16" x14ac:dyDescent="0.25">
@@ -81427,7 +82096,7 @@
       </c>
       <c r="M16">
         <f ca="1">AVERAGEIFS(NEET[Total_Marks_720],NEET[Age of Student],Analysis!L16,NEET[Attempt_No],Analysis!$M$5)</f>
-        <v>403.4</v>
+        <v>405.69230769230768</v>
       </c>
     </row>
     <row r="17" spans="2:5" x14ac:dyDescent="0.25">
@@ -81555,6 +82224,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{48FC0009-96EA-4892-A2E6-B44E824092D9}">
+  <sheetPr codeName="Sheet6"/>
   <dimension ref="B2:Y34"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -82287,7 +82957,131 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5E9CCAB4-0E8F-40EA-ADA1-5C5B62F5928A}">
+  <sheetPr codeName="Sheet1"/>
+  <dimension ref="B2:J8"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="2" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B2" t="s">
+        <v>1075</v>
+      </c>
+      <c r="C2">
+        <v>0</v>
+      </c>
+      <c r="E2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="F2">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="3" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B3" t="s">
+        <v>1076</v>
+      </c>
+      <c r="C3">
+        <v>10</v>
+      </c>
+      <c r="E3" t="s">
+        <v>1082</v>
+      </c>
+      <c r="F3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B4" t="s">
+        <v>1077</v>
+      </c>
+      <c r="C4">
+        <v>25</v>
+      </c>
+      <c r="E4" t="s">
+        <v>1084</v>
+      </c>
+      <c r="F4">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="5" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B5" t="s">
+        <v>1078</v>
+      </c>
+      <c r="C5">
+        <v>50</v>
+      </c>
+      <c r="J5" t="s">
+        <v>1066</v>
+      </c>
+    </row>
+    <row r="6" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B6" t="s">
+        <v>1079</v>
+      </c>
+      <c r="C6">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="7" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B7" t="s">
+        <v>1080</v>
+      </c>
+      <c r="C7">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="8" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B8" t="s">
+        <v>1081</v>
+      </c>
+      <c r="C8">
+        <f>SUM(C3:C7)</f>
+        <v>345</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+  <ignoredErrors>
+    <ignoredError sqref="C8" formulaRange="1"/>
+  </ignoredErrors>
+  <drawing r:id="rId2"/>
+  <legacyDrawing r:id="rId3"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x14">
+      <controls>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <control shapeId="7171" r:id="rId4" name="Spinner 3">
+              <controlPr defaultSize="0" autoPict="0">
+                <anchor moveWithCells="1" sizeWithCells="1">
+                  <from>
+                    <xdr:col>6</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>1</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>7</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>2</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+      </controls>
+    </mc:Choice>
+  </mc:AlternateContent>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{16E1DB5B-33F9-447B-9B97-9B5868C4D070}">
+  <sheetPr codeName="Sheet7"/>
   <dimension ref="A1:H16"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
